--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -511,22 +511,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -569,58 +569,178 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -724,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="L5" t="n">
-        <v>3.16</v>
+        <v>3.46</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -801,22 +801,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -859,22 +859,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A Coruna</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>24</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -917,22 +917,62 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -975,22 +975,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>18</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/real-betis-balompie.xlsx
+++ b/new-stats/real-betis-balompie.xlsx
@@ -1033,22 +1033,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
